--- a/BD/Carga masiva/Presentacion/Codelco/1_Carga_Inventario_Codelco.xlsx
+++ b/BD/Carga masiva/Presentacion/Codelco/1_Carga_Inventario_Codelco.xlsx
@@ -2,6 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -22,50 +23,32 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="dd-mm-yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="1"/>
       <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FF6732F4"/>
+      <color rgb="006732F4"/>
       <sz val="16"/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <color rgb="FF68738A"/>
-      <sz val="11"/>
+      <b val="1"/>
+      <color rgb="0017223B"/>
     </font>
     <font>
-      <name val="Calibri"/>
       <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FF17223B"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="FF68738A"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -74,21 +57,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2EFFF"/>
+        <fgColor rgb="00EAF4FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFEAF4FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6732F4"/>
+        <fgColor rgb="006732F4"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -96,43 +74,26 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFE2E7F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -212,27 +173,27 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Vacío: se numera solo (BOD-&lt;n&gt;). No se puede cambiar después.</t>
+        <t>Opcional. Vacío: se numera solo (BOD-&lt;n&gt;). No se puede cambiar después. Ejemplo: EJEMPLO-CENTRAL</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Cómo la reconoce la gente.</t>
+        <t>Obligatoria. Cómo la reconoce la gente. Ejemplo: Bodega Central</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Tal como aparece en la hoja PLANTAS. Vea la hoja PLANTAS.</t>
+        <t>Obligatoria. Tal como aparece en la hoja PLANTAS. Ejemplo: Planta Renca</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Para qué se usa.</t>
+        <t>Opcional. Para qué se usa. Ejemplo: Repuestos críticos de línea 1</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>FEFO (vence primero), FIFO (entró primero) o LIFO. Vacío: FEFO. Valores: FEFO, FIFO, LIFO.</t>
+        <t>Opcional. FEFO (vence primero), FIFO (entró primero) o LIFO. Vacío: FEFO. Ejemplo: FEFO</t>
       </text>
     </comment>
   </commentList>
@@ -247,37 +208,42 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código o nombre de la bodega (de la base o de la hoja BODEGAS).</t>
+        <t>Obligatoria. Código o nombre de la bodega (de la base o de la hoja BODEGAS). Ejemplo: EJEMPLO-CENTRAL</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>Pasillo, Sala, Zona, Sector… Vacío: Pasillo. Si no existe, se crea.</t>
+        <t>Opcional. Pasillo, Sala, Zona, Sector… Vacío: Pasillo. Si no existe, se crea. Ejemplo: Pasillo</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Código del área: 1 a 3 letras (A, B, AB). Obligatorio si no escribe el código.</t>
+        <t>Opcional. Código del área: 1 a 3 letras (A, B, AB). Obligatorio si no escribe el código. Ejemplo: A</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Número del rack en el área. Vacío: el siguiente libre.</t>
+        <t>Opcional. Número del rack en el área. Vacío: el siguiente libre. Ejemplo: 1</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Solo si ya tiene un código impreso. Vacío: se arma solo.</t>
+        <t>Opcional. Solo si ya tiene un código impreso. Vacío: se arma solo.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Vacío: «Pasillo A · Rack 01» (con el tipo de área).</t>
+        <t>Opcional. Vacío: «Pasillo A · Rack 01» (con el tipo de área).</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Carga admisible por nivel. Vacío: 1.000 kg.</t>
+        <t>Opcional. Carga admisible por nivel. Vacío: 1.000 kg. Ejemplo: 1000</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Cuántos niveles tiene el rack (1 a 10). Vacío: 4. Ejemplo: 4</t>
       </text>
     </comment>
   </commentList>
@@ -292,92 +258,102 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>Vacío: se numera solo. Con un código existente, se actualiza.</t>
+        <t>Opcional. Vacío: se numera solo. Con un código existente, se actualiza. Ejemplo: EJEMPLO-ROD-001</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Obligatorio para un repuesto nuevo.</t>
+        <t>Obligatoria. Obligatorio para un repuesto nuevo. Ejemplo: Rodamiento 6205-2RS1</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Como en la hoja UNIDADES (UNIDAD, LITRO, METRO...). Vea la hoja UNIDADES.</t>
+        <t>Obligatoria. Como en la hoja UNIDADES (UNIDAD, LITRO, METRO...). Ejemplo: UNIDAD</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Se normaliza solo: «skf» y «SKF» son el mismo.</t>
+        <t>Opcional. Se normaliza solo: «skf» y «SKF» son el mismo. Ejemplo: SKF</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Código del fabricante.</t>
+        <t>Opcional. Código del fabricante. Ejemplo: 6205-2RS1</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>SI: cada ingreso pide lote y vencimiento. Valores: SI, NO.</t>
+        <t>Opcional. SI: cada ingreso pide lote y vencimiento. Ejemplo: NO</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>SI: se gasta y no vuelve a bodega. Valores: SI, NO.</t>
+        <t>Opcional. SI: se gasta y no vuelve a bodega. Ejemplo: NO</t>
       </text>
     </comment>
     <comment ref="H1" authorId="0" shapeId="0">
       <text>
-        <t>SI: puede volver reparado. Valores: SI, NO.</t>
+        <t>Opcional. SI: puede volver reparado. Ejemplo: NO</t>
       </text>
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>En pesos. Referencial.</t>
+        <t>Opcional. En pesos. Referencial. Ejemplo: 8500</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Horas de marcha que declara el fabricante.</t>
+        <t>Opcional. Horas de marcha que declara el fabricante. Ejemplo: 8000</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>Días de calendario.</t>
+        <t>Opcional. Días de calendario.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Maniobras.</t>
+        <t>Opcional. Maniobras.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Detalle técnico.</t>
+        <t>Opcional. Detalle técnico. Ejemplo: Una hilera de bolas, sello de contacto.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
-        <t>Solo al actualizar: NO lo da de baja. Valores: SI, NO.</t>
+        <t>Opcional. Solo al actualizar: NO lo da de baja. Ejemplo: SI</t>
       </text>
     </comment>
     <comment ref="O1" authorId="0" shapeId="0">
       <text>
-        <t>Código o nombre, como en la hoja TIPOS. Vea la hoja TIPOS.</t>
+        <t>Opcional. Categoría del repuesto (Rodamientos, Motores…). Si no existe, se crea. Ejemplo: Rodamientos</t>
       </text>
     </comment>
     <comment ref="P1" authorId="0" shapeId="0">
       <text>
-        <t>Excepción del repuesto. «Según bodega» la quita. Valores: Según bodega, FEFO, FIFO, LIFO.</t>
+        <t>Opcional. Excepción del repuesto. «Según bodega» la quita.</t>
       </text>
     </comment>
     <comment ref="Q1" authorId="0" shapeId="0">
       <text>
-        <t>Para el mapa 3D.</t>
+        <t>Opcional. Para el mapa 3D.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Opcional. </t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Opcional. </t>
       </text>
     </comment>
     <comment ref="T1" authorId="0" shapeId="0">
       <text>
-        <t>Por unidad. El mapa avisa la sobrecarga del nivel.</t>
+        <t>Opcional. Por unidad. El mapa avisa la sobrecarga del nivel.</t>
       </text>
     </comment>
   </commentList>
@@ -392,27 +368,32 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código del repuesto (de la base o de la hoja REPUESTOS).</t>
+        <t>Obligatoria. Código del repuesto (de la base o de la hoja REPUESTOS). Ejemplo: EJEMPLO-ROD-001</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código o nombre de la bodega.</t>
+        <t>Obligatoria. Código o nombre de la bodega. Ejemplo: EJEMPLO-CENTRAL</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Bajo este número el repuesto queda en alerta.</t>
+        <t>Obligatoria. Bajo este número el repuesto queda en alerta. Ejemplo: 2</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Hasta cuánto se repone.</t>
+        <t>Opcional. Hasta cuánto se repone. Ejemplo: 10</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Cuándo pedir: entre el mínimo y el máximo.</t>
+        <t>Opcional. Cuándo pedir: entre el mínimo y el máximo. Ejemplo: 4</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Opcional. </t>
       </text>
     </comment>
   </commentList>
@@ -427,37 +408,62 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código del repuesto.</t>
+        <t>Obligatoria. Código del repuesto. Ejemplo: EJEMPLO-ROD-001</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código o nombre de la bodega.</t>
+        <t>Obligatoria. Código o nombre de la bodega. Ejemplo: EJEMPLO-CENTRAL</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Código o nombre del rack. Obligatorio si la bodega tiene racks.</t>
+        <t>Opcional. Código del pasillo o área del rack (A, B…). Con él, RACK es solo el número. Ejemplo: A</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Mayor que cero.</t>
+        <t>Opcional. Con PASILLO: el número del rack (1, 2…). Sin PASILLO: su código o nombre. Obligatorio si la bodega tiene racks. Ejemplo: 1</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>En pesos. Valoriza el stock.</t>
+        <t>Opcional. Nivel del rack donde queda (1 = el más bajo, hasta los NIVELES del rack). Ejemplo: 1</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>Obligatorio si el repuesto controla lote.</t>
+        <t>Opcional. Posición dentro del nivel, de 1 a 30. Vacío: la siguiente libre.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>Fecha de vencimiento del lote.</t>
+        <t>Opcional. 0 = delante, 1 = detrás. Vacío: 0. Ejemplo: 0</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Obligatoria. Mayor que cero. Ejemplo: 12</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. En pesos. Valoriza el stock. Ejemplo: 8500</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Obligatorio si el repuesto controla lote.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Opcional. Fecha de vencimiento del lote.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Opcional. </t>
       </text>
     </comment>
   </commentList>
@@ -472,17 +478,22 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código o nombre del repuesto (de la base o de la hoja REPUESTOS).</t>
+        <t>Obligatoria. Código o nombre del repuesto (de la base o de la hoja REPUESTOS). Ejemplo: EJEMPLO-ROD-001</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>OBLIGATORIA. Código o nombre del activo, como en la hoja ACTIVOS EXISTENTES. Vea la hoja ACTIVOS EXISTENTES.</t>
+        <t>Obligatoria. Código o nombre del activo, como en la hoja ACTIVOS EXISTENTES.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>Si sirve a una pieza del activo: su nombre. Vacío: al activo entero.</t>
+        <t>Opcional. Si sirve a una pieza del activo: su nombre. Vacío: al activo entero.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Opcional. </t>
       </text>
     </comment>
   </commentList>
@@ -778,7 +789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -792,115 +803,67 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Bodegas, racks, repuestos, umbrales, el stock con que parte cada bodega y en qué equipos sirve cada repuesto. · Demostración: Codelco · Concentradora Cerro Alto (datos inventados).</t>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bodegas, racks con sus niveles, repuestos, umbrales y el stock inicial ubicado por PASILLO · RACK · NIVEL · POSICION. · Demostración: Codelco · Concentradora Cerro Alto (datos inventados).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>1. Complete las hojas en el orden en que aparecen: cada una puede nombrar lo que crea una hoja anterior de este mismo archivo.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1. Una hoja por paso, en el orden en que aparecen. Los encabezados MORADOS son obligatorios; los celestes, opcionales.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>2. Las columnas con encabezado MORADO son obligatorias para un registro nuevo; las celestes son opcionales.</t>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2. Pase el mouse por cada encabezado para ver qué escribir.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>3. Pase el mouse por cada encabezado para ver qué escribir. Las listas desplegables y las hojas de ayuda (al final) muestran los valores válidos.</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>3. Con el mismo código se ACTUALIZA: las celdas vacías conservan lo que había. Volver a cargar no duplica.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>4. La fila que empieza con EJEMPLO se ignora: bórrela o déjela.</t>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>4. Primero REVISE (no escribe nada) y después CARGUE. Una fila con error no detiene la carga.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>5. Con el mismo código se ACTUALIZA: las celdas con dato reemplazan y las vacías conservan lo que había. Volver a cargar el archivo no duplica.</t>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>5. Complete las hojas en orden: BODEGAS, RACKS, REPUESTOS, UMBRALES y STOCK INICIAL.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>6. Primero REVISE: SIGMA dice qué pasará con cada fila (crear, actualizar, error) sin escribir nada. Después cargue.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   RACKS: cada rack es PASILLO + NUMERO y declara cuántos NIVELES tiene.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>7. Una fila con error no detiene la carga: se informa con su hoja, fila, columna y motivo, y se descarga en Excel para corregir.</t>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   STOCK INICIAL: PASILLO (A, B…), RACK (el número del rack en ese pasillo), NIVEL (1 = el más bajo), POSICION y FILA ubican el repuesto en su casillero.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>HOJAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>BODEGAS — Una fila por bodega. Con el mismo código (o el mismo nombre, si no lleva código) se actualiza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>RACKS — Una fila por rack. Sin código, se arma como en el mapa 3D: &lt;prefijo&gt;-&lt;área&gt;-R&lt;nn&gt;, desde el siguiente número libre del área (pasillo, sala, zona…).</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>REPUESTOS — Las mismas columnas de la carga de repuestos de siempre, más método y medidas. Con el mismo código se actualiza: las celdas vacías conservan lo que había.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>UMBRALES — Mínimo, máximo y punto de reposición de cada repuesto en cada bodega. Si ya existe, se reemplaza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>STOCK INICIAL — Lo que hay hoy en cada bodega y rack. Entra como un ingreso, una sola vez: si ya hay stock en ese rack (y lote), la fila se rechaza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>COMPATIBILIDADES — En qué equipos o componentes sirve cada repuesto. El activo tiene que existir (carga de Activos). Si ya está vinculado, se omite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   El TIPO del repuesto es de la empresa: si no existe, se crea con ese nombre.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -910,134 +873,128 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" style="8" min="1" max="1"/>
-    <col width="28" customWidth="1" style="8" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" style="8" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>CODIGO</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>PLANTA</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>METODO SALIDA</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Bodega Central de Repuestos Cerro Alto</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Concentradora Cerro Alto</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Rodamientos, motores, variadores, sensores, sellos y válvulas</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>FIFO</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Bodega de Piezas de Desgaste</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>Concentradora Cerro Alto</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Revestimientos de molinos y chancadores, bolas de acero, rodillos y banda transportadora</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>FIFO</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Bodega de Lubricantes y Reactivos</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Concentradora Cerro Alto</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Aceites, grasas y reactivos de flotación, con lote y vencimiento</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>FEFO</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="E2:E100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"FEFO,FIFO,LIFO"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1046,94 +1003,102 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" style="8" min="1" max="1"/>
-    <col width="14" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10" customWidth="1" style="8" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" style="8" min="5" max="5"/>
-    <col width="26" customWidth="1" style="8" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>BODEGA</t>
         </is>
       </c>
-      <c r="B1" s="9" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>TIPO AREA</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>AREA</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>NUMERO</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>CODIGO</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CARGA NIVEL KG</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>NIVELES</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="n">
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>800</v>
       </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1144,19 +1109,22 @@
       <c r="G3" t="n">
         <v>800</v>
       </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1167,19 +1135,22 @@
       <c r="G4" t="n">
         <v>800</v>
       </c>
+      <c r="H4" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1190,19 +1161,22 @@
       <c r="G5" t="n">
         <v>800</v>
       </c>
+      <c r="H5" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1213,19 +1187,22 @@
       <c r="G6" t="n">
         <v>1200</v>
       </c>
+      <c r="H6" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
@@ -1236,19 +1213,22 @@
       <c r="G7" t="n">
         <v>1200</v>
       </c>
+      <c r="H7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1259,19 +1239,22 @@
       <c r="G8" t="n">
         <v>5000</v>
       </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1282,19 +1265,22 @@
       <c r="G9" t="n">
         <v>5000</v>
       </c>
+      <c r="H9" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1305,19 +1291,22 @@
       <c r="G10" t="n">
         <v>5000</v>
       </c>
+      <c r="H10" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1328,19 +1317,22 @@
       <c r="G11" t="n">
         <v>2000</v>
       </c>
+      <c r="H11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1351,19 +1343,22 @@
       <c r="G12" t="n">
         <v>2000</v>
       </c>
+      <c r="H12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Pasillo</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
@@ -1373,6 +1368,9 @@
       </c>
       <c r="G13" t="n">
         <v>2000</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1384,191 +1382,203 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:T25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="8" min="1" max="1"/>
-    <col width="34" customWidth="1" style="8" min="2" max="2"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" style="8" min="4" max="4"/>
-    <col width="18" customWidth="1" style="8" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="36" customWidth="1" style="8" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="16" customWidth="1" min="17" max="17"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="15" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="9" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>CODIGO</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>NOMBRE</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>FABRICANTE</t>
         </is>
       </c>
-      <c r="E1" s="9" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>MODELO</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>CONTROLA LOTE</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>CONSUMIBLE</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>REPARABLE</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>COSTO REFERENCIA</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>VIDA UTIL HORAS</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>VIDA UTIL DIAS</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>VIDA UTIL CICLOS</t>
         </is>
       </c>
-      <c r="M1" s="9" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>DESCRIPCION</t>
         </is>
       </c>
-      <c r="N1" s="6" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>HABILITADO</t>
         </is>
       </c>
-      <c r="O1" s="6" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>TIPO</t>
         </is>
       </c>
-      <c r="P1" s="6" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>METODO SALIDA</t>
         </is>
       </c>
-      <c r="Q1" s="6" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>LARGO CM</t>
         </is>
       </c>
-      <c r="R1" s="6" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>ANCHO CM</t>
         </is>
       </c>
-      <c r="S1" s="6" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>ALTO CM</t>
         </is>
       </c>
-      <c r="T1" s="6" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>PESO KG</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-SAG</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Revestimiento (liner) de descarga del molino SAG</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D2" s="10" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>Metso</t>
         </is>
       </c>
-      <c r="E2" s="10" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Outotec SAG-DL36</t>
         </is>
       </c>
-      <c r="F2" s="10" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G2" s="10" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H2" s="10" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="I2" s="7" t="n">
+      <c r="I2" t="n">
         <v>4800000</v>
       </c>
-      <c r="J2" s="7" t="n">
+      <c r="J2" t="n">
         <v>9000</v>
       </c>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="inlineStr">
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Placa de acero al cromo-molibdeno que protege la descarga del molino SAG; se cambia por desgaste en la parada mayor.</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="O2" s="7" t="n"/>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>Revestimientos</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
+        </is>
+      </c>
       <c r="Q2" t="n">
         <v>180</v>
       </c>
@@ -1583,42 +1593,42 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-BOL</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Revestimiento (liner) del molino de bolas</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>Metso</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Outotec BM-L26</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1629,9 +1639,24 @@
       <c r="J3" t="n">
         <v>9000</v>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Placa de revestimiento del casco del molino de bolas; se mide su espesor en cada parada.</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Revestimientos</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -1648,42 +1673,42 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-CHA</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Manto del chancador giratorio primario</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>Metso</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Superior 60-89</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1694,9 +1719,24 @@
       <c r="J4" t="n">
         <v>7000</v>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>Pieza de desgaste móvil del chancador giratorio primario; se cambia junto con el cóncavo.</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Desgaste de chancado</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1713,42 +1753,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CA-CON-CHA</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Cóncavo del chancador giratorio primario</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Metso</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Superior 60-89 C</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1759,9 +1799,24 @@
       <c r="J5" t="n">
         <v>7000</v>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>Pieza de desgaste fija del chancador giratorio primario; se cambia por segmentos.</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>Desgaste de chancado</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1778,42 +1833,42 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CA-BOL-5</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Bolas de acero forjado 5 pulgadas</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>KILOGRAMO</t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Moly-Cop</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Forjada 5"</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1821,9 +1876,24 @@
       <c r="I6" t="n">
         <v>1450</v>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>Medio de molienda del molino SAG y del molino de bolas; se repone según el consumo diario.</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>Medios de molienda</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1840,42 +1910,42 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-23240</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Rodamiento esférico de rodillos 23240 CC/W33</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>SKF</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>23240 CC/W33</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1886,9 +1956,24 @@
       <c r="J7" t="n">
         <v>30000</v>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>Rodamiento del eje principal del chancador; criticidad alta, no hay otro igual en la planta.</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>Rodamientos</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -1905,42 +1990,42 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-22232</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Rodamiento esférico de rodillos 22232 E</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>FAG</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>22232-E1-K</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -1951,9 +2036,24 @@
       <c r="J8" t="n">
         <v>30000</v>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Rodamiento de la polea tractora de la correa y del soplador de flotación.</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Rodamientos</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q8" t="n">
@@ -1970,42 +2070,42 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CA-RODILLO-152</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Rodillo de carga Ø152 mm para correa transportadora</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D9" s="8" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Rulmeca</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>PSV-152x1000</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2016,9 +2116,24 @@
       <c r="J9" t="n">
         <v>40000</v>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Rodillo de carga de la correa CV-101; se cambia por trabado o desgaste de la carcasa.</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Transporte de mineral</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -2035,42 +2150,42 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CA-BANDA-ST1600</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Banda transportadora ST-1600 (por metro)</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>METRO</t>
         </is>
       </c>
-      <c r="D10" s="8" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Fenner Dunlop</t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>ST-1600 EP</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2081,9 +2196,24 @@
       <c r="J10" t="n">
         <v>60000</v>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Banda con cables de acero para empalmes y reparaciones de la correa CV-101; se compra y se controla por metro.</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Transporte de mineral</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -2100,42 +2230,42 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CA-POL-TRAC</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Polea tractora Ø800 con enlainado</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Continental</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>PT-800</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G11" s="8" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2143,9 +2273,24 @@
       <c r="I11" t="n">
         <v>9800000</v>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Polea de accionamiento con enlainado cerámico; se envía a reparar cuando pierde adherencia.</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Transporte de mineral</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -2162,42 +2307,42 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CA-IMP-PULPA</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Impulsor de bomba de pulpa 8x6</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Weir Minerals</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Warman AH 8/6</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2208,9 +2353,24 @@
       <c r="J12" t="n">
         <v>4500</v>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Impulsor de la bomba de pulpa; se puede reparar o reemplazar.</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Bombas de pulpa</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -2227,42 +2387,42 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-PULPA</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Revestimiento (liner) de bomba de pulpa</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D13" s="8" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Weir Minerals</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Warman AH 8/6 LN</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2273,9 +2433,24 @@
       <c r="J13" t="n">
         <v>4500</v>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Revestimiento de la carcasa de la bomba de pulpa.</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>Revestimientos</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -2292,42 +2467,42 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CA-SEL-PULPA</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Sello mecánico para bomba de pulpa</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>John Crane</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Type 5610</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2338,9 +2513,27 @@
       <c r="J14" t="n">
         <v>6000</v>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="K14" t="n">
+        <v>730</v>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Sello mecánico de la bomba de pulpa; se cambia ante fuga.</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>Bombas de pulpa</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -2357,42 +2550,42 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CA-MOT-250</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Motor eléctrico trifásico 250 kW 6 kV 4 polos</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>M3BM 400</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2403,9 +2596,24 @@
       <c r="J15" t="n">
         <v>90000</v>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Motor de reserva de 250 kW para bombas y correas; se repara en taller externo.</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Motores y variadores</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2422,42 +2630,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CA-VAR-500</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Variador de frecuencia de media tensión 500 kW</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D16" s="8" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>ACS1000</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2465,9 +2673,24 @@
       <c r="I16" t="n">
         <v>65000000</v>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Variador de media tensión de reserva; se repara con el fabricante.</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Motores y variadores</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q16" t="n">
@@ -2484,42 +2707,42 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CA-CON-MV</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Contactor de media tensión 7,2 kV</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>3TL6</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G17" s="8" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2527,9 +2750,27 @@
       <c r="I17" t="n">
         <v>3200000</v>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="L17" t="n">
+        <v>100000</v>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Contactor de media tensión de los tableros de la subestación.</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Electricidad de media tensión</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q17" t="n">
@@ -2546,42 +2787,42 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-VIB</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Sensor de vibración IEPE con cable</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>SKF</t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>CMSS 2200</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2589,9 +2830,24 @@
       <c r="I18" t="n">
         <v>215000</v>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Sensor de vibración de las variables de monitoreo de chancador y soplador.</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Instrumentación</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q18" t="n">
@@ -2608,42 +2864,42 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-NIV</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Transmisor de nivel ultrasónico</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Endress+Hauser</t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Prosonic FMU90</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G19" s="8" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2651,9 +2907,24 @@
       <c r="I19" t="n">
         <v>1380000</v>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Transmisor de nivel de las celdas de flotación y del espesador.</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Instrumentación</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2670,42 +2941,42 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CA-VAL-CUC</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Válvula de cuchillo DN200 para pulpa</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D20" s="8" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Weir Minerals</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Clarkson KGA</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="8" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
@@ -2713,9 +2984,27 @@
       <c r="I20" t="n">
         <v>2400000</v>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="L20" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Válvula de aislación de las líneas de pulpa.</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Válvulas y mangueras</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q20" t="n">
@@ -2732,42 +3021,42 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-HID</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Manguera hidráulica de 2 pulgadas alta presión (por metro)</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>METRO</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>Gates</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>MegaSys 2"</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="8" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2778,9 +3067,27 @@
       <c r="J21" t="n">
         <v>12000</v>
       </c>
-      <c r="N21" s="8" t="inlineStr">
+      <c r="K21" t="n">
+        <v>1460</v>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>Manguera hidráulica de alta presión; se corta a medida.</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr">
+        <is>
+          <t>Válvulas y mangueras</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>FIFO</t>
         </is>
       </c>
       <c r="Q21" t="n">
@@ -2797,42 +3104,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-HID</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Aceite hidráulico ISO VG 46 (tambor 200 L)</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>LITRO</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>Shell</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Tellus S2 M 46</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2840,9 +3147,27 @@
       <c r="I22" t="n">
         <v>3900</v>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="K22" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Aceite hidráulico para el sistema de ajuste del chancador y las unidades hidráulicas.</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Lubricantes</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>FEFO</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2859,42 +3184,42 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-ENG</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Aceite para engranajes ISO VG 320 (tambor 200 L)</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>LITRO</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>Mobil</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Mobilgear 600 XP 320</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2902,9 +3227,27 @@
       <c r="I23" t="n">
         <v>4800</v>
       </c>
-      <c r="N23" s="8" t="inlineStr">
+      <c r="K23" t="n">
+        <v>1095</v>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Aceite para los reductores y el sistema de lubricación del molino SAG; se controla por lote y vencimiento.</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Lubricantes</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>FEFO</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -2921,42 +3264,42 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>CA-GRA-EP2</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Grasa EP-2 base litio cartucho 400 g</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>UNIDAD</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>Klüber</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Centoplex 2 EP</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -2964,9 +3307,27 @@
       <c r="I24" t="n">
         <v>6900</v>
       </c>
-      <c r="N24" s="8" t="inlineStr">
+      <c r="K24" t="n">
+        <v>730</v>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Grasa de extrema presión para los cojinetes de los molinos.</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Lubricantes</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>FEFO</t>
         </is>
       </c>
       <c r="Q24" t="n">
@@ -2983,42 +3344,42 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>CA-QUI-XAN</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Xantato amílico de potasio (tambor 200 kg)</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>KILOGRAMO</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
         <is>
           <t>Qiborax</t>
         </is>
       </c>
-      <c r="E25" s="8" t="inlineStr">
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>PAX Premium</t>
         </is>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>SI</t>
         </is>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
@@ -3026,9 +3387,27 @@
       <c r="I25" t="n">
         <v>2350</v>
       </c>
-      <c r="N25" s="8" t="inlineStr">
+      <c r="K25" t="n">
+        <v>365</v>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Colector de la flotación de cobre; se controla por lote y vencimiento.</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>SI</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Reactivos de flotación</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>FEFO</t>
         </is>
       </c>
       <c r="Q25" t="n">
@@ -3045,23 +3424,6 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
-    <dataValidation sqref="F2:F100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="G2:G100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H2:H100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SI,NO"</formula1>
-    </dataValidation>
-    <dataValidation sqref="P2:P100000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Según bodega,FEFO,FIFO,LIFO"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -3070,81 +3432,85 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="8" min="1" max="1"/>
-    <col width="20" customWidth="1" style="8" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" style="8" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>REPUESTO</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>BODEGA</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>MINIMO</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>MAXIMO</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>PUNTO REPOSICION</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>OBSERVACION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-SAG</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="n">
+      <c r="D2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="E2" t="n">
         <v>3</v>
       </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-BOL</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3158,14 +3524,19 @@
       <c r="E3" t="n">
         <v>6</v>
       </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-CHA</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3179,14 +3550,19 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CA-CON-CHA</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3200,14 +3576,19 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CA-BOL-5</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3221,14 +3602,19 @@
       <c r="E6" t="n">
         <v>40000</v>
       </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-23240</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3242,14 +3628,19 @@
       <c r="E7" t="n">
         <v>2</v>
       </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-22232</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3263,14 +3654,19 @@
       <c r="E8" t="n">
         <v>3</v>
       </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CA-RODILLO-152</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3284,14 +3680,19 @@
       <c r="E9" t="n">
         <v>50</v>
       </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CA-BANDA-ST1600</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3305,14 +3706,19 @@
       <c r="E10" t="n">
         <v>60</v>
       </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CA-POL-TRAC</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3326,14 +3732,19 @@
       <c r="E11" t="n">
         <v>1</v>
       </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CA-IMP-PULPA</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3347,14 +3758,19 @@
       <c r="E12" t="n">
         <v>2</v>
       </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-PULPA</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
@@ -3368,14 +3784,19 @@
       <c r="E13" t="n">
         <v>3</v>
       </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CA-SEL-PULPA</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3389,14 +3810,19 @@
       <c r="E14" t="n">
         <v>3</v>
       </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CA-MOT-250</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3410,14 +3836,19 @@
       <c r="E15" t="n">
         <v>1</v>
       </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CA-VAR-500</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3431,14 +3862,19 @@
       <c r="E16" t="n">
         <v>1</v>
       </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CA-CON-MV</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3452,14 +3888,19 @@
       <c r="E17" t="n">
         <v>2</v>
       </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-VIB</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3473,14 +3914,19 @@
       <c r="E18" t="n">
         <v>6</v>
       </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-NIV</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3494,14 +3940,19 @@
       <c r="E19" t="n">
         <v>2</v>
       </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CA-VAL-CUC</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3515,14 +3966,19 @@
       <c r="E20" t="n">
         <v>2</v>
       </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-HID</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
@@ -3536,14 +3992,19 @@
       <c r="E21" t="n">
         <v>40</v>
       </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-HID</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
@@ -3557,14 +4018,19 @@
       <c r="E22" t="n">
         <v>800</v>
       </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-ENG</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
@@ -3578,14 +4044,19 @@
       <c r="E23" t="n">
         <v>800</v>
       </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>CA-GRA-EP2</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
@@ -3599,14 +4070,19 @@
       <c r="E24" t="n">
         <v>48</v>
       </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>CA-QUI-XAN</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
@@ -3619,6 +4095,11 @@
       </c>
       <c r="E25" t="n">
         <v>1200</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Mínimo = consumo de un mes; reposición con el proveedor habitual</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3630,764 +4111,1075 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="8" min="1" max="1"/>
-    <col width="20" customWidth="1" style="8" min="2" max="2"/>
-    <col width="20" customWidth="1" style="8" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" style="8" min="6" max="6"/>
-    <col width="13" customWidth="1" style="13" min="7" max="7"/>
-    <col width="26" customWidth="1" style="8" min="8" max="8"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>REPUESTO</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>BODEGA</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>PASILLO</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>RACK</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>NIVEL</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>POSICION</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>FILA</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>CANTIDAD</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>COSTO UNITARIO</t>
         </is>
       </c>
-      <c r="F1" s="9" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>LOTE</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>VENCE</t>
         </is>
       </c>
-      <c r="H1" s="9" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>OBSERVACION</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="10" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-SAG</t>
         </is>
       </c>
-      <c r="B2" s="10" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C2" s="10" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 01</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="n">
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="n">
+      <c r="I2" t="n">
         <v>4800000</v>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="L2" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-BOL</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>8</v>
       </c>
-      <c r="E3" t="n">
+      <c r="I3" t="n">
         <v>2650000</v>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-CHA</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>21500000</v>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CA-CON-CHA</t>
         </is>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>18900000</v>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CA-BOL-5</t>
         </is>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 01</t>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
         <v>52000</v>
       </c>
-      <c r="E6" t="n">
+      <c r="I6" t="n">
         <v>1450</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-23240</t>
         </is>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 01</t>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="E7" t="n">
+      <c r="I7" t="n">
         <v>1850000</v>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CA-ROD-22232</t>
         </is>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 01</t>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
+      <c r="I8" t="n">
         <v>740000</v>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CA-RODILLO-152</t>
         </is>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
         <v>85</v>
       </c>
-      <c r="E9" t="n">
+      <c r="I9" t="n">
         <v>96000</v>
       </c>
-      <c r="H9" s="8" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CA-BANDA-ST1600</t>
         </is>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>3</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
         <v>80</v>
       </c>
-      <c r="E10" t="n">
+      <c r="I10" t="n">
         <v>430000</v>
       </c>
-      <c r="H10" s="8" t="inlineStr">
+      <c r="L10" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CA-POL-TRAC</t>
         </is>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
         <v>9800000</v>
       </c>
-      <c r="H11" s="8" t="inlineStr">
+      <c r="L11" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CA-IMP-PULPA</t>
         </is>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" t="n">
         <v>3900000</v>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CA-LIN-PULPA</t>
         </is>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>BOD-DES</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
         <v>4</v>
       </c>
-      <c r="E13" t="n">
+      <c r="I13" t="n">
         <v>2700000</v>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="L13" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CA-SEL-PULPA</t>
         </is>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
+      <c r="I14" t="n">
         <v>1250000</v>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="L14" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CA-MOT-250</t>
         </is>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo B · Rack 01</t>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>1</v>
       </c>
       <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
         <v>28500000</v>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="L15" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CA-VAR-500</t>
         </is>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo B · Rack 02</t>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>65000000</v>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="L16" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CA-CON-MV</t>
         </is>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
         <v>3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="I17" t="n">
         <v>3200000</v>
       </c>
-      <c r="H17" s="8" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-VIB</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 04</t>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
         <v>9</v>
       </c>
-      <c r="E18" t="n">
+      <c r="I18" t="n">
         <v>215000</v>
       </c>
-      <c r="H18" s="8" t="inlineStr">
+      <c r="L18" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CA-SEN-NIV</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 04</t>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>2</v>
       </c>
       <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2</v>
+      </c>
+      <c r="I19" t="n">
         <v>1380000</v>
       </c>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="L19" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CA-VAL-CUC</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo B · Rack 02</t>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
         <v>2400000</v>
       </c>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CA-MAN-HID</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>BOD-CEN</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 04</t>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>55</v>
       </c>
-      <c r="E21" t="n">
+      <c r="I21" t="n">
         <v>62000</v>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-HID</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 01</t>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
         <v>1200</v>
       </c>
-      <c r="E22" t="n">
+      <c r="I22" t="n">
         <v>3900</v>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="J22" s="4" t="inlineStr">
         <is>
           <t>LOTE-2026-HID</t>
         </is>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="K22" s="5" t="n">
         <v>46934</v>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="L22" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CA-ACE-ENG</t>
         </is>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 02</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
         <v>1000</v>
       </c>
-      <c r="E23" t="n">
+      <c r="I23" t="n">
         <v>4800</v>
       </c>
-      <c r="F23" s="8" t="inlineStr">
+      <c r="J23" s="4" t="inlineStr">
         <is>
           <t>LOTE-2026-ENG</t>
         </is>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="K23" s="5" t="n">
         <v>47026</v>
       </c>
-      <c r="H23" s="8" t="inlineStr">
+      <c r="L23" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>CA-GRA-EP2</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
         <v>72</v>
       </c>
-      <c r="E24" t="n">
+      <c r="I24" t="n">
         <v>6900</v>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>LOTE-2026-EP2</t>
         </is>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="K24" s="5" t="n">
         <v>46843</v>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="L24" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>CA-QUI-XAN</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>BOD-LUB</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Pasillo A · Rack 03</t>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
         <v>1600</v>
       </c>
-      <c r="E25" t="n">
+      <c r="I25" t="n">
         <v>2350</v>
       </c>
-      <c r="F25" s="8" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>LOTE-2026-XAN</t>
         </is>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="K25" s="5" t="n">
         <v>46752</v>
       </c>
-      <c r="H25" s="8" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t>Stock inicial al implementar SIGMA</t>
         </is>
@@ -4402,43 +5194,39 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="FF6732F4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" style="8" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" style="8" min="3" max="3"/>
-    <col width="26" customWidth="1" style="8" min="4" max="4"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>REPUESTO</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>ACTIVO</t>
         </is>
       </c>
-      <c r="C1" s="9" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>COMPONENTE</t>
         </is>
       </c>
-      <c r="D1" s="9" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>OBSERVACION</t>
         </is>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
